--- a/Auswertung2510(inBearbeitung).xlsx
+++ b/Auswertung2510(inBearbeitung).xlsx
@@ -84,7 +84,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -92,13 +92,25 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -110,13 +122,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Gut" xfId="1" builtinId="26"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -444,7 +459,7 @@
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A16" t="s">
+      <c r="A16" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C16">
@@ -493,7 +508,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A21" t="s">
+      <c r="A21" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C21">
@@ -524,7 +539,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A22" t="s">
+      <c r="A22" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C22">

--- a/Auswertung2510(inBearbeitung).xlsx
+++ b/Auswertung2510(inBearbeitung).xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="20">
   <si>
     <t>Enthalten</t>
   </si>
@@ -68,16 +68,22 @@
     <t>Werke</t>
   </si>
   <si>
-    <t>Schröder</t>
-  </si>
-  <si>
     <t>Rieger</t>
   </si>
   <si>
     <t>Hettner</t>
   </si>
   <si>
-    <t>keine Werke gefunden</t>
+    <t>Orte</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>Personen handannotiert</t>
+  </si>
+  <si>
+    <t>Schröder (hochgerechnet)</t>
   </si>
 </sst>
 </file>
@@ -410,7 +416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A13:K32"/>
+  <dimension ref="A13:K39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="13" spans="1:11" x14ac:dyDescent="0.4">
@@ -451,7 +457,7 @@
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A15" t="s">
+      <c r="A15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C15">
@@ -459,156 +465,230 @@
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C16">
+      <c r="C17">
         <v>399</v>
       </c>
-      <c r="D16">
+      <c r="D17">
         <v>149</v>
       </c>
-      <c r="E16">
+      <c r="E17">
         <v>205</v>
       </c>
-      <c r="F16">
+      <c r="F17">
         <v>34</v>
       </c>
-      <c r="G16">
+      <c r="G17">
         <v>11</v>
       </c>
-      <c r="H16">
+      <c r="H17">
         <v>0.42090395480226001</v>
       </c>
-      <c r="I16">
-        <f>D16/C16</f>
+      <c r="I17">
+        <f>D17/C17</f>
         <v>0.37343358395989973</v>
       </c>
-      <c r="J16">
-        <f>2*(H16*I16)/(H16+I16)</f>
+      <c r="J17">
+        <f>2*(H17*I17)/(H17+I17)</f>
         <v>0.39575033200531212</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A17" t="s">
-        <v>13</v>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <v>36</v>
+      </c>
+      <c r="C18">
+        <v>22</v>
+      </c>
+      <c r="D18">
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="C22">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A24" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24">
+        <v>234</v>
+      </c>
+      <c r="D24">
+        <v>153</v>
+      </c>
+      <c r="E24">
+        <v>45</v>
+      </c>
+      <c r="F24">
+        <v>16</v>
+      </c>
+      <c r="G24">
+        <v>18</v>
+      </c>
+      <c r="H24">
+        <v>0.77272727272727304</v>
+      </c>
+      <c r="I24">
+        <f>D24/C24</f>
+        <v>0.65384615384615385</v>
+      </c>
+      <c r="J24">
+        <f>2*(H24*I24)/(H24+I24)</f>
+        <v>0.70833333333333348</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25">
+        <v>52</v>
+      </c>
+      <c r="D25">
+        <v>38</v>
+      </c>
+      <c r="E25">
         <v>14</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A21" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21">
-        <v>234</v>
-      </c>
-      <c r="D21">
-        <v>153</v>
-      </c>
-      <c r="E21">
-        <v>45</v>
-      </c>
-      <c r="F21">
-        <v>16</v>
-      </c>
-      <c r="G21">
-        <v>18</v>
-      </c>
-      <c r="H21">
-        <v>0.77272727272727304</v>
-      </c>
-      <c r="I21">
-        <f>D21/C21</f>
-        <v>0.65384615384615385</v>
-      </c>
-      <c r="J21">
-        <f>2*(H21*I21)/(H21+I21)</f>
-        <v>0.70833333333333348</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A22" s="1" t="s">
+      <c r="H25">
+        <v>0.73076923076923095</v>
+      </c>
+      <c r="I25">
+        <f>D25/D24</f>
+        <v>0.24836601307189543</v>
+      </c>
+      <c r="J25">
+        <f>2*(H25*I25)/(H25+I25)</f>
+        <v>0.37073170731707322</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A26" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C22">
-        <v>52</v>
-      </c>
-      <c r="D22">
-        <v>38</v>
-      </c>
-      <c r="E22">
+      <c r="B26">
+        <v>15</v>
+      </c>
+      <c r="C26" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
         <v>14</v>
-      </c>
-      <c r="H22">
-        <v>0.73076923076923095</v>
-      </c>
-      <c r="I22">
-        <f>D22/D21</f>
-        <v>0.24836601307189543</v>
-      </c>
-      <c r="J22">
-        <f>2*(H22*I22)/(H22+I22)</f>
-        <v>0.37073170731707322</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A24" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A25" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A26" t="s">
-        <v>12</v>
-      </c>
-      <c r="B26">
-        <v>214</v>
-      </c>
-      <c r="C26">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A27" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A30" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30">
+        <v>420</v>
+      </c>
+      <c r="D30">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A31" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A30" t="s">
+      <c r="C31">
+        <v>151</v>
+      </c>
+      <c r="D31">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A32" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C32" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A35" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A31" t="s">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A36" t="s">
+        <v>18</v>
+      </c>
+      <c r="B36">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A37" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A32" t="s">
+      <c r="C37">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A38" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A39" t="s">
         <v>13</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C39" t="s">
         <v>17</v>
       </c>
     </row>

--- a/Auswertung2510(inBearbeitung).xlsx
+++ b/Auswertung2510(inBearbeitung).xlsx
@@ -13,6 +13,7 @@
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
+    <sheet name="Tabelle2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="46">
   <si>
     <t>Enthalten</t>
   </si>
@@ -59,15 +60,15 @@
     <t>Hülk</t>
   </si>
   <si>
-    <t>Gesamt</t>
-  </si>
-  <si>
     <t>Personen</t>
   </si>
   <si>
     <t>Werke</t>
   </si>
   <si>
+    <t>Schröder</t>
+  </si>
+  <si>
     <t>Rieger</t>
   </si>
   <si>
@@ -83,7 +84,85 @@
     <t>Personen handannotiert</t>
   </si>
   <si>
-    <t>Schröder (hochgerechnet)</t>
+    <t>0.3953488372093023</t>
+  </si>
+  <si>
+    <t>0.45</t>
+  </si>
+  <si>
+    <t>0.42090784044016505</t>
+  </si>
+  <si>
+    <t>precision</t>
+  </si>
+  <si>
+    <t>recall</t>
+  </si>
+  <si>
+    <t>f1</t>
+  </si>
+  <si>
+    <t>0.2718978102189781</t>
+  </si>
+  <si>
+    <t>0.7563451776649747</t>
+  </si>
+  <si>
+    <t>0.4</t>
+  </si>
+  <si>
+    <t>0.39655172413793105</t>
+  </si>
+  <si>
+    <t>0.6065934065934065</t>
+  </si>
+  <si>
+    <t>1.2897196261682242</t>
+  </si>
+  <si>
+    <t>Recall &gt;1 ergibt sich aus unterschiedlicher Bewertung richtig/falsch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schröder </t>
+  </si>
+  <si>
+    <t>Werke Liste</t>
+  </si>
+  <si>
+    <t>0.3333333333333333</t>
+  </si>
+  <si>
+    <t>0.3055555555555556</t>
+  </si>
+  <si>
+    <t>0.31884057971014496</t>
+  </si>
+  <si>
+    <t>0.11428571428571428</t>
+  </si>
+  <si>
+    <t>0.1</t>
+  </si>
+  <si>
+    <t>0.10666666666666666</t>
+  </si>
+  <si>
+    <t>0.4175824175824176</t>
+  </si>
+  <si>
+    <t>0.07156308851224105</t>
+  </si>
+  <si>
+    <t>0.12218649517684886</t>
+  </si>
+  <si>
+    <t>0.4846153846153846</t>
+  </si>
+  <si>
+    <t>0.9402985074626866</t>
+  </si>
+  <si>
+    <t>0.6395939086294417</t>
   </si>
 </sst>
 </file>
@@ -132,9 +211,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Gut" xfId="1" builtinId="26"/>
@@ -416,283 +496,457 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A13:K39"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="2" max="2" width="3.84375" customWidth="1"/>
+    <col min="3" max="3" width="4.4609375" customWidth="1"/>
+    <col min="4" max="4" width="5.61328125" customWidth="1"/>
+    <col min="5" max="7" width="0" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="0" hidden="1" customWidth="1"/>
+  </cols>
   <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3">
+        <v>197</v>
+      </c>
+      <c r="C3">
+        <v>399</v>
+      </c>
+      <c r="D3">
+        <v>149</v>
+      </c>
+      <c r="E3">
+        <v>205</v>
+      </c>
+      <c r="F3">
+        <v>34</v>
+      </c>
+      <c r="G3">
+        <v>11</v>
+      </c>
+      <c r="H3">
+        <v>0.42090395480226001</v>
+      </c>
+      <c r="I3">
+        <f>D3/C3</f>
+        <v>0.37343358395989973</v>
+      </c>
+      <c r="J3">
+        <f>2*(H3*I3)/(H3+I3)</f>
+        <v>0.39575033200531212</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4">
+        <v>36</v>
+      </c>
+      <c r="C4">
+        <v>22</v>
+      </c>
+      <c r="D4">
+        <v>11</v>
+      </c>
+      <c r="H4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6">
+        <v>31</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="H6" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6" t="s">
+        <v>38</v>
+      </c>
+      <c r="J6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A7" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8">
+        <v>290</v>
+      </c>
+      <c r="C8">
+        <v>234</v>
+      </c>
+      <c r="D8">
+        <v>153</v>
+      </c>
+      <c r="E8">
+        <v>45</v>
+      </c>
+      <c r="F8">
+        <v>16</v>
+      </c>
+      <c r="G8">
+        <v>18</v>
+      </c>
+      <c r="H8">
+        <v>0.77272727272727304</v>
+      </c>
+      <c r="I8">
+        <f>D8/C8</f>
+        <v>0.65384615384615385</v>
+      </c>
+      <c r="J8">
+        <f>2*(H8*I8)/(H8+I8)</f>
+        <v>0.70833333333333348</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9">
+        <v>33</v>
+      </c>
+      <c r="C9">
+        <v>52</v>
+      </c>
+      <c r="D9">
+        <v>38</v>
+      </c>
+      <c r="E9">
+        <v>14</v>
+      </c>
+      <c r="H9">
+        <v>0.73076923076923095</v>
+      </c>
+      <c r="I9">
+        <f>D9/D8</f>
+        <v>0.24836601307189543</v>
+      </c>
+      <c r="J9">
+        <f>2*(H9*I9)/(H9+I9)</f>
+        <v>0.37073170731707322</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10">
+        <v>531</v>
+      </c>
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11">
+        <v>53</v>
+      </c>
+      <c r="D11">
+        <v>38</v>
+      </c>
+      <c r="H11" t="s">
+        <v>40</v>
+      </c>
+      <c r="I11" t="s">
+        <v>41</v>
+      </c>
+      <c r="J11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A12" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="B13" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" t="s">
-        <v>1</v>
-      </c>
-      <c r="D13" t="s">
-        <v>2</v>
-      </c>
-      <c r="E13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F13" t="s">
-        <v>4</v>
-      </c>
-      <c r="G13" t="s">
-        <v>5</v>
+      <c r="A13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>214</v>
+      </c>
+      <c r="C13">
+        <v>420</v>
+      </c>
+      <c r="D13">
+        <v>276</v>
       </c>
       <c r="H13" t="s">
-        <v>6</v>
-      </c>
-      <c r="I13" t="s">
-        <v>7</v>
+        <v>28</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="J13" t="s">
-        <v>8</v>
-      </c>
-      <c r="K13" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
-        <v>10</v>
+      <c r="A14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14">
+        <v>151</v>
+      </c>
+      <c r="D14">
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15">
+        <v>67</v>
+      </c>
+      <c r="C15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A16" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16">
+        <v>67</v>
+      </c>
+      <c r="D16">
+        <v>63</v>
+      </c>
+      <c r="H16" t="s">
+        <v>43</v>
+      </c>
+      <c r="I16" t="s">
+        <v>44</v>
+      </c>
+      <c r="J16" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A17" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A19" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C15">
-        <v>2043</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A16" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A17" s="1" t="s">
+      <c r="C19">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A20" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A21" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C17">
-        <v>399</v>
-      </c>
-      <c r="D17">
-        <v>149</v>
-      </c>
-      <c r="E17">
-        <v>205</v>
-      </c>
-      <c r="F17">
-        <v>34</v>
-      </c>
-      <c r="G17">
-        <v>11</v>
-      </c>
-      <c r="H17">
-        <v>0.42090395480226001</v>
-      </c>
-      <c r="I17">
-        <f>D17/C17</f>
-        <v>0.37343358395989973</v>
-      </c>
-      <c r="J17">
-        <f>2*(H17*I17)/(H17+I17)</f>
-        <v>0.39575033200531212</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A18" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18">
-        <v>36</v>
-      </c>
-      <c r="C18">
-        <v>22</v>
-      </c>
-      <c r="D18">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A19" t="s">
-        <v>13</v>
-      </c>
-      <c r="B19">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A21" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="C22">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A23" t="s">
-        <v>18</v>
-      </c>
-      <c r="B23">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A24" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C24">
-        <v>234</v>
-      </c>
-      <c r="D24">
-        <v>153</v>
-      </c>
-      <c r="E24">
-        <v>45</v>
-      </c>
-      <c r="F24">
-        <v>16</v>
-      </c>
-      <c r="G24">
-        <v>18</v>
-      </c>
-      <c r="H24">
-        <v>0.77272727272727304</v>
-      </c>
-      <c r="I24">
-        <f>D24/C24</f>
-        <v>0.65384615384615385</v>
-      </c>
-      <c r="J24">
-        <f>2*(H24*I24)/(H24+I24)</f>
-        <v>0.70833333333333348</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A25" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25">
-        <v>52</v>
-      </c>
-      <c r="D25">
-        <v>38</v>
-      </c>
-      <c r="E25">
-        <v>14</v>
-      </c>
-      <c r="H25">
-        <v>0.73076923076923095</v>
-      </c>
-      <c r="I25">
-        <f>D25/D24</f>
-        <v>0.24836601307189543</v>
-      </c>
-      <c r="J25">
-        <f>2*(H25*I25)/(H25+I25)</f>
-        <v>0.37073170731707322</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A26" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B26">
-        <v>15</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="B21">
+        <v>5</v>
+      </c>
+      <c r="C21" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A28" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A29" t="s">
-        <v>18</v>
-      </c>
-      <c r="C29">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A30" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C30">
-        <v>420</v>
-      </c>
-      <c r="D30">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A31" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31">
-        <v>151</v>
-      </c>
-      <c r="D31">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A32" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C32" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A34" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A35" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A36" t="s">
-        <v>18</v>
-      </c>
-      <c r="B36">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A37" t="s">
-        <v>12</v>
-      </c>
-      <c r="C37">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A38" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A39" t="s">
-        <v>13</v>
-      </c>
-      <c r="C39" t="s">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A22" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" t="s">
         <v>17</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="25.3046875" customWidth="1"/>
+    <col min="3" max="4" width="33.4609375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Auswertung2510(inBearbeitung).xlsx
+++ b/Auswertung2510(inBearbeitung).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16457" windowHeight="5546"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16457" windowHeight="5546" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -169,7 +169,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -178,24 +178,28 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -209,15 +213,16 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Gut" xfId="1" builtinId="26"/>
+    <cellStyle name="Erklärender Text" xfId="1" builtinId="53"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -499,9 +504,10 @@
   <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="3.84375" customWidth="1"/>
-    <col min="3" max="3" width="4.4609375" customWidth="1"/>
-    <col min="4" max="4" width="5.61328125" customWidth="1"/>
+    <col min="1" max="1" width="19.07421875" customWidth="1"/>
+    <col min="2" max="2" width="15.61328125" customWidth="1"/>
+    <col min="3" max="3" width="12.23046875" customWidth="1"/>
+    <col min="4" max="4" width="13.765625" customWidth="1"/>
     <col min="5" max="7" width="0" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="0" hidden="1" customWidth="1"/>
   </cols>
@@ -539,12 +545,12 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>11</v>
       </c>
       <c r="B3">
@@ -578,7 +584,7 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>16</v>
       </c>
       <c r="B4">
@@ -601,7 +607,7 @@
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>12</v>
       </c>
       <c r="B5">
@@ -609,7 +615,7 @@
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>33</v>
       </c>
       <c r="C6">
@@ -629,12 +635,12 @@
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="2" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>11</v>
       </c>
       <c r="B8">
@@ -668,7 +674,7 @@
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>16</v>
       </c>
       <c r="B9">
@@ -696,7 +702,7 @@
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>12</v>
       </c>
       <c r="B10">
@@ -707,7 +713,7 @@
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>33</v>
       </c>
       <c r="C11">
@@ -727,12 +733,12 @@
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>11</v>
       </c>
       <c r="B13">
@@ -747,7 +753,7 @@
       <c r="H13" t="s">
         <v>28</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="I13" s="1" t="s">
         <v>30</v>
       </c>
       <c r="J13" t="s">
@@ -755,7 +761,7 @@
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>16</v>
       </c>
       <c r="C14">
@@ -766,7 +772,7 @@
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>12</v>
       </c>
       <c r="B15">
@@ -777,7 +783,7 @@
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>33</v>
       </c>
       <c r="C16">
@@ -797,52 +803,60 @@
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="3" t="s">
         <v>15</v>
       </c>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="3">
         <v>53</v>
       </c>
+      <c r="C18" s="3"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C19">
+      <c r="B19" s="3"/>
+      <c r="C19" s="3">
         <v>381</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="3">
         <v>5</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="3" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C22" t="s">
+      <c r="B22" s="3"/>
+      <c r="C22" s="3" t="s">
         <v>17</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -927,7 +941,7 @@
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B14" t="s">

--- a/Auswertung2510(inBearbeitung).xlsx
+++ b/Auswertung2510(inBearbeitung).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16457" windowHeight="5546" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16457" windowHeight="5546"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="47">
   <si>
     <t>Enthalten</t>
   </si>
@@ -163,6 +163,9 @@
   </si>
   <si>
     <t>0.6395939086294417</t>
+  </si>
+  <si>
+    <t>Gesamt</t>
   </si>
 </sst>
 </file>
@@ -215,11 +218,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Erklärender Text" xfId="1" builtinId="53"/>
@@ -501,7 +505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="19.07421875" customWidth="1"/>
@@ -764,8 +768,11 @@
       <c r="A14" t="s">
         <v>16</v>
       </c>
+      <c r="B14">
+        <v>65</v>
+      </c>
       <c r="C14">
-        <v>151</v>
+        <v>287</v>
       </c>
       <c r="D14">
         <v>63</v>
@@ -802,55 +809,102 @@
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A17" s="3" t="s">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A17" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A18" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18">
+        <v>701</v>
+      </c>
+      <c r="C18">
+        <v>1053</v>
+      </c>
+      <c r="D18">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19">
+        <v>134</v>
+      </c>
+      <c r="C19">
+        <v>361</v>
+      </c>
+      <c r="D19">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A20" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20">
+        <v>638</v>
+      </c>
+      <c r="C20">
+        <v>151</v>
+      </c>
+      <c r="D20">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A21" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A18" s="3" t="s">
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A22" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B22" s="3">
         <v>53</v>
       </c>
-      <c r="C18" s="3"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A19" s="3" t="s">
+      <c r="C22" s="3"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A23" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3">
+      <c r="B23" s="3"/>
+      <c r="C23" s="3">
         <v>381</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A20" s="3" t="s">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A24" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A21" s="3" t="s">
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A25" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B25" s="3">
         <v>5</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C25" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A22" s="3" t="s">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A26" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3" t="s">
+      <c r="B26" s="3"/>
+      <c r="C26" s="3" t="s">
         <v>17</v>
       </c>
     </row>
